--- a/data/normalization.xlsx
+++ b/data/normalization.xlsx
@@ -9044,7 +9044,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B765"/>
+  <dimension ref="A1:B764"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10112,63 +10112,63 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ca</v>
+        <v>cabestrillo</v>
       </c>
       <c r="B134" t="str">
-        <v>coa</v>
+        <v>estribeira</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>cabestrillo</v>
+        <v>cabildo</v>
       </c>
       <c r="B135" t="str">
-        <v>estribeira</v>
+        <v>cabido</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>cabildo</v>
+        <v>cabilla</v>
       </c>
       <c r="B136" t="str">
-        <v>cabido</v>
+        <v>cavilla</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>cabilla</v>
+        <v>cabofa</v>
       </c>
       <c r="B137" t="str">
-        <v>cavilla</v>
+        <v>cagofo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>cabofa</v>
+        <v>caborco</v>
       </c>
       <c r="B138" t="str">
-        <v>cagofo</v>
+        <v>cavorco</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>caborco</v>
+        <v>caboza</v>
       </c>
       <c r="B139" t="str">
-        <v>cavorco</v>
+        <v>cavoza</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>caboza</v>
+        <v>cachifo</v>
       </c>
       <c r="B140" t="str">
-        <v>cavoza</v>
+        <v>cacifo</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>cachifo</v>
+        <v>cachifro</v>
       </c>
       <c r="B141" t="str">
         <v>cacifo</v>
@@ -10176,18 +10176,18 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>cachifro</v>
+        <v>cadaseu</v>
       </c>
       <c r="B142" t="str">
-        <v>cacifo</v>
+        <v>cadanseu</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>cadaseu</v>
+        <v>caella</v>
       </c>
       <c r="B143" t="str">
-        <v>cadanseu</v>
+        <v>quella</v>
       </c>
     </row>
     <row r="144">
@@ -10195,7 +10195,7 @@
         <v>caella</v>
       </c>
       <c r="B144" t="str">
-        <v>quella</v>
+        <v>quenlla</v>
       </c>
     </row>
     <row r="145">
@@ -10208,79 +10208,79 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>caella</v>
+        <v>caiada</v>
       </c>
       <c r="B146" t="str">
-        <v>quenlla</v>
+        <v>caxata</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>caiada</v>
+        <v>caladeiro</v>
       </c>
       <c r="B147" t="str">
-        <v>caxata</v>
+        <v>caladoiro</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>caladeiro</v>
+        <v>calamar</v>
       </c>
       <c r="B148" t="str">
-        <v>caladoiro</v>
+        <v>lura</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>calamar</v>
+        <v>calaveira</v>
       </c>
       <c r="B149" t="str">
-        <v>lura</v>
+        <v>caveira</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>calaveira</v>
+        <v>calificable</v>
       </c>
       <c r="B150" t="str">
-        <v>caveira</v>
+        <v>cualificable</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>calificable</v>
+        <v>calificación</v>
       </c>
       <c r="B151" t="str">
-        <v>cualificable</v>
+        <v>cualificación</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>calificación</v>
+        <v>calificar</v>
       </c>
       <c r="B152" t="str">
-        <v>cualificación</v>
+        <v>cualificar</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>calificar</v>
+        <v>campeonato</v>
       </c>
       <c r="B153" t="str">
-        <v>cualificar</v>
+        <v>campionato</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>campeonato</v>
+        <v>canadiña</v>
       </c>
       <c r="B154" t="str">
-        <v>campionato</v>
+        <v>quenlla</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>canadiña</v>
+        <v>canaleta</v>
       </c>
       <c r="B155" t="str">
         <v>quenlla</v>
@@ -10288,242 +10288,242 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>canaleta</v>
+        <v>canalón</v>
       </c>
       <c r="B156" t="str">
-        <v>quenlla</v>
+        <v>caleiro</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>canalón</v>
+        <v>candado</v>
       </c>
       <c r="B157" t="str">
-        <v>caleiro</v>
+        <v>cadeado</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>candado</v>
+        <v>candión</v>
       </c>
       <c r="B158" t="str">
-        <v>cadeado</v>
+        <v>candeón</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>candión</v>
+        <v>cangrena</v>
       </c>
       <c r="B159" t="str">
-        <v>candeón</v>
+        <v>gangrena</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>cangrena</v>
+        <v>canilla</v>
       </c>
       <c r="B160" t="str">
-        <v>gangrena</v>
+        <v>canela</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>canilla</v>
+        <v>canuto</v>
       </c>
       <c r="B161" t="str">
-        <v>canela</v>
+        <v>canudo</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>canuto</v>
+        <v>cañón</v>
       </c>
       <c r="B162" t="str">
-        <v>canudo</v>
+        <v>canón</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>cañón</v>
+        <v>cañonazo</v>
       </c>
       <c r="B163" t="str">
-        <v>canón</v>
+        <v>canonazo</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>cañonazo</v>
+        <v>cañonear</v>
       </c>
       <c r="B164" t="str">
-        <v>canonazo</v>
+        <v>canonear</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cañonear</v>
+        <v>cañoneo</v>
       </c>
       <c r="B165" t="str">
-        <v>canonear</v>
+        <v>canoneo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>cañoneo</v>
+        <v>carbunco</v>
       </c>
       <c r="B166" t="str">
-        <v>canoneo</v>
+        <v>carafuncho</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>carbunco</v>
+        <v>carcoma</v>
       </c>
       <c r="B167" t="str">
-        <v>carafuncho</v>
+        <v>caruncho</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>carcoma</v>
+        <v>careo</v>
       </c>
       <c r="B168" t="str">
-        <v>caruncho</v>
+        <v>acareo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>careo</v>
+        <v>carepa</v>
       </c>
       <c r="B169" t="str">
-        <v>acareo</v>
+        <v>carapa</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>carepa</v>
+        <v>cartílago</v>
       </c>
       <c r="B170" t="str">
-        <v>carapa</v>
+        <v>cartilaxe</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>cartílago</v>
+        <v>cen</v>
       </c>
       <c r="B171" t="str">
-        <v>cartilaxe</v>
+        <v>sen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>cen</v>
+        <v>centinela</v>
       </c>
       <c r="B172" t="str">
-        <v>sen</v>
+        <v>sentinela</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>centinela</v>
+        <v>cercelo</v>
       </c>
       <c r="B173" t="str">
-        <v>sentinela</v>
+        <v>sarcelo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>cercelo</v>
+        <v>cerne</v>
       </c>
       <c r="B174" t="str">
-        <v>sarcelo</v>
+        <v>cerna</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>cerne</v>
+        <v>cerrollo</v>
       </c>
       <c r="B175" t="str">
-        <v>cerna</v>
+        <v>ferrollo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>cerrollo</v>
+        <v>chambrico</v>
       </c>
       <c r="B176" t="str">
-        <v>ferrollo</v>
+        <v>chambaril</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>chambrico</v>
+        <v>champán</v>
       </c>
       <c r="B177" t="str">
-        <v>chambaril</v>
+        <v>champaña</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>champán</v>
+        <v>chaparrón</v>
       </c>
       <c r="B178" t="str">
-        <v>champaña</v>
+        <v>ballón</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>chaparrón</v>
+        <v>chelín</v>
       </c>
       <c r="B179" t="str">
-        <v>ballón</v>
+        <v>xilin</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>chelín</v>
+        <v>chiíta</v>
       </c>
       <c r="B180" t="str">
-        <v>xilin</v>
+        <v>xiíta</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>chiíta</v>
+        <v>chilaba</v>
       </c>
       <c r="B181" t="str">
-        <v>xiíta</v>
+        <v>xilaba</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>chilaba</v>
+        <v>chimenea</v>
       </c>
       <c r="B182" t="str">
-        <v>xilaba</v>
+        <v>cheminea</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>chimenea</v>
+        <v>chipirón</v>
       </c>
       <c r="B183" t="str">
-        <v>cheminea</v>
+        <v>luriña</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>chipirón</v>
+        <v>chombo</v>
       </c>
       <c r="B184" t="str">
-        <v>luriña</v>
+        <v>chumbo</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>chombo</v>
+        <v>choupo</v>
       </c>
       <c r="B185" t="str">
-        <v>chumbo</v>
+        <v>chopo</v>
       </c>
     </row>
     <row r="186">
@@ -10536,1634 +10536,1634 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>choupo</v>
+        <v>chuleta</v>
       </c>
       <c r="B187" t="str">
-        <v>chopo</v>
+        <v>costeleta</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>chuleta</v>
+        <v>churume</v>
       </c>
       <c r="B188" t="str">
-        <v>costeleta</v>
+        <v>chorume</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>churume</v>
+        <v>ciar</v>
       </c>
       <c r="B189" t="str">
-        <v>chorume</v>
+        <v>cear</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>ciar</v>
+        <v>cibela</v>
       </c>
       <c r="B190" t="str">
-        <v>cear</v>
+        <v>fibela</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>cibela</v>
+        <v>cimborrio</v>
       </c>
       <c r="B191" t="str">
-        <v>fibela</v>
+        <v>ciborio</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>cimborrio</v>
+        <v>cincel</v>
       </c>
       <c r="B192" t="str">
-        <v>ciborio</v>
+        <v>cicel</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>cincel</v>
+        <v>cinxa</v>
       </c>
       <c r="B193" t="str">
-        <v>cicel</v>
+        <v>cinsa</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>cinxa</v>
+        <v>cipaio</v>
       </c>
       <c r="B194" t="str">
-        <v>cinsa</v>
+        <v>sipaio</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>cipaio</v>
+        <v>cipela</v>
       </c>
       <c r="B195" t="str">
-        <v>sipaio</v>
+        <v>erisipela</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>cipela</v>
+        <v>ciste</v>
       </c>
       <c r="B196" t="str">
-        <v>erisipela</v>
+        <v>quiste</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>ciste</v>
+        <v>coallar</v>
       </c>
       <c r="B197" t="str">
-        <v>quiste</v>
+        <v>callar</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>coallar</v>
+        <v>cobarde</v>
       </c>
       <c r="B198" t="str">
-        <v>callar</v>
+        <v>covarde</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>cobarde</v>
+        <v>cobardemente</v>
       </c>
       <c r="B199" t="str">
-        <v>covarde</v>
+        <v>covardemente</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>cobardemente</v>
+        <v>cobardía</v>
       </c>
       <c r="B200" t="str">
-        <v>covardemente</v>
+        <v>covardía</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cobardía</v>
+        <v>cochinada</v>
       </c>
       <c r="B201" t="str">
-        <v>covardía</v>
+        <v>cochada</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cochinada</v>
+        <v>cocodrilo</v>
       </c>
       <c r="B202" t="str">
-        <v>cochada</v>
+        <v>crocodilo</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>cocodrilo</v>
+        <v>cofradía</v>
       </c>
       <c r="B203" t="str">
-        <v>crocodilo</v>
+        <v>confraría</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>cofradía</v>
+        <v>cogote</v>
       </c>
       <c r="B204" t="str">
-        <v>confraría</v>
+        <v>cocote</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cogote</v>
+        <v>coincar</v>
       </c>
       <c r="B205" t="str">
-        <v>cocote</v>
+        <v>cuincar</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>coincar</v>
+        <v>coiñar</v>
       </c>
       <c r="B206" t="str">
-        <v>cuincar</v>
+        <v>cuiñar</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>coiñar</v>
+        <v>colchete</v>
       </c>
       <c r="B207" t="str">
-        <v>cuiñar</v>
+        <v>corchete</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>colchete</v>
+        <v>coletazo</v>
       </c>
       <c r="B208" t="str">
-        <v>corchete</v>
+        <v>rabexada</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>coletazo</v>
+        <v>coletilla</v>
       </c>
       <c r="B209" t="str">
-        <v>rabexada</v>
+        <v>apostila</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>coletilla</v>
+        <v>collarín</v>
       </c>
       <c r="B210" t="str">
-        <v>apostila</v>
+        <v>colariño</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>collarín</v>
+        <v>columpio</v>
       </c>
       <c r="B211" t="str">
-        <v>colariño</v>
+        <v>randeeira</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>columpio</v>
+        <v>comulgar</v>
       </c>
       <c r="B212" t="str">
-        <v>randeeira</v>
+        <v>comungar</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>comulgar</v>
+        <v>comunión</v>
       </c>
       <c r="B213" t="str">
-        <v>comungar</v>
+        <v>comuñón</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>comunión</v>
+        <v>concebir</v>
       </c>
       <c r="B214" t="str">
-        <v>comuñón</v>
+        <v>concibir</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>concebir</v>
+        <v>confite</v>
       </c>
       <c r="B215" t="str">
-        <v>concibir</v>
+        <v>confeito</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>confite</v>
+        <v>conquerer</v>
       </c>
       <c r="B216" t="str">
-        <v>confeito</v>
+        <v>conquistar</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>conquerer</v>
+        <v>de contado</v>
       </c>
       <c r="B217" t="str">
-        <v>conquistar</v>
+        <v>decontado</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>de contado</v>
+        <v>de contiño</v>
       </c>
       <c r="B218" t="str">
-        <v>decontado</v>
+        <v>decontino</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>de contiño</v>
+        <v>contraseña</v>
       </c>
       <c r="B219" t="str">
-        <v>decontino</v>
+        <v>contrasinal</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>contraseña</v>
+        <v>conxa</v>
       </c>
       <c r="B220" t="str">
-        <v>contrasinal</v>
+        <v>coxa</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>conxa</v>
+        <v>corbata</v>
       </c>
       <c r="B221" t="str">
-        <v>coxa</v>
+        <v>gravata</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>corbata</v>
+        <v>corbeta</v>
       </c>
       <c r="B222" t="str">
-        <v>gravata</v>
+        <v>corveta</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>corbeta</v>
+        <v>corcho</v>
       </c>
       <c r="B223" t="str">
-        <v>corveta</v>
+        <v>cortiza</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>corcho</v>
+        <v>corondollo</v>
       </c>
       <c r="B224" t="str">
-        <v>cortiza</v>
+        <v>colondrollo</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>corondollo</v>
+        <v>corrada</v>
       </c>
       <c r="B225" t="str">
-        <v>colondrollo</v>
+        <v>currada</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>corrada</v>
+        <v>corral</v>
       </c>
       <c r="B226" t="str">
-        <v>currada</v>
+        <v>curral</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>corral</v>
+        <v>corresponsal</v>
       </c>
       <c r="B227" t="str">
-        <v>curral</v>
+        <v>correspondente</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>corresponsal</v>
+        <v>coruto</v>
       </c>
       <c r="B228" t="str">
-        <v>correspondente</v>
+        <v>curuto</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>coruto</v>
+        <v>coruxa</v>
       </c>
       <c r="B229" t="str">
-        <v>curuto</v>
+        <v>curuxa</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>coruxa</v>
+        <v>costar</v>
       </c>
       <c r="B230" t="str">
-        <v>curuxa</v>
+        <v>custar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>costar</v>
+        <v>de cote</v>
       </c>
       <c r="B231" t="str">
-        <v>custar</v>
+        <v>decote</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>de cote</v>
+        <v>a cotío</v>
       </c>
       <c r="B232" t="str">
-        <v>decote</v>
+        <v>acotío</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>a cotío</v>
+        <v>de cotío</v>
       </c>
       <c r="B233" t="str">
-        <v>acotío</v>
+        <v>decotío</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>de cotío</v>
+        <v>cresta</v>
       </c>
       <c r="B234" t="str">
-        <v>decotío</v>
+        <v>crista</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>cresta</v>
+        <v>croquis</v>
       </c>
       <c r="B235" t="str">
-        <v>crista</v>
+        <v>esbozo</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>croquis</v>
+        <v>cruce</v>
       </c>
       <c r="B236" t="str">
-        <v>esbozo</v>
+        <v>cruzamento</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>cruce</v>
+        <v>cuaderna</v>
       </c>
       <c r="B237" t="str">
-        <v>cruzamento</v>
+        <v>caderna</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>cuaderna</v>
+        <v>cuádruple</v>
       </c>
       <c r="B238" t="str">
-        <v>caderna</v>
+        <v>cuádruplo</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>cuádruple</v>
+        <v>cuallar</v>
       </c>
       <c r="B239" t="str">
-        <v>cuádruplo</v>
+        <v>callar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>cuallar</v>
+        <v>cuaño</v>
       </c>
       <c r="B240" t="str">
-        <v>callar</v>
+        <v>caño</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>cuaño</v>
+        <v>cuartana</v>
       </c>
       <c r="B241" t="str">
-        <v>caño</v>
+        <v>cuartá</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>cuartana</v>
+        <v>cuatri-</v>
       </c>
       <c r="B242" t="str">
-        <v>cuartá</v>
+        <v>cuadri-</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>cuatri-</v>
+        <v>cubilete</v>
       </c>
       <c r="B243" t="str">
-        <v>cuadri-</v>
+        <v>gobelete</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>cubilete</v>
+        <v>cucurucho</v>
       </c>
       <c r="B244" t="str">
-        <v>gobelete</v>
+        <v>cornete</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>cucurucho</v>
+        <v>culeiro</v>
       </c>
       <c r="B245" t="str">
-        <v>cornete</v>
+        <v>coleiro</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>culeiro</v>
+        <v>cupo</v>
       </c>
       <c r="B246" t="str">
-        <v>coleiro</v>
+        <v>cota</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>cupo</v>
+        <v>curricán</v>
       </c>
       <c r="B247" t="str">
-        <v>cota</v>
+        <v>corricán</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>curricán</v>
+        <v>cutrillón</v>
       </c>
       <c r="B248" t="str">
-        <v>corricán</v>
+        <v>cotellón</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>cutrillón</v>
+        <v>cutuluvía</v>
       </c>
       <c r="B249" t="str">
-        <v>cotellón</v>
+        <v>cotovía</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>cutuluvía</v>
+        <v>cuxillo</v>
       </c>
       <c r="B250" t="str">
-        <v>cotovía</v>
+        <v>coxillo</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>cuxillo</v>
+        <v>de reollo</v>
       </c>
       <c r="B251" t="str">
-        <v>coxillo</v>
+        <v>de esguello</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>de reollo</v>
+        <v>debecer</v>
       </c>
       <c r="B252" t="str">
-        <v>de esguello</v>
+        <v>devecer</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>debecer</v>
+        <v>deborcar</v>
       </c>
       <c r="B253" t="str">
-        <v>devecer</v>
+        <v>debrocar</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>deborcar</v>
+        <v>deboucar</v>
       </c>
       <c r="B254" t="str">
-        <v>debrocar</v>
+        <v>demoucar</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>deboucar</v>
+        <v>decir</v>
       </c>
       <c r="B255" t="str">
-        <v>demoucar</v>
+        <v>dicir</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>decir</v>
+        <v>decomisar</v>
       </c>
       <c r="B256" t="str">
-        <v>dicir</v>
+        <v>comisar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>decomisar</v>
+        <v>decomiso</v>
       </c>
       <c r="B257" t="str">
-        <v>comisar</v>
+        <v>comiso</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>decomiso</v>
+        <v>de mais</v>
       </c>
       <c r="B258" t="str">
-        <v>comiso</v>
+        <v>de máis</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>de mais</v>
+        <v>demisión</v>
       </c>
       <c r="B259" t="str">
-        <v>de máis</v>
+        <v>dimisión</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>demisión</v>
+        <v>demitir</v>
       </c>
       <c r="B260" t="str">
-        <v>dimisión</v>
+        <v>dimitir</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>demitir</v>
+        <v>depositaría</v>
       </c>
       <c r="B261" t="str">
-        <v>dimitir</v>
+        <v>tesouraría</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>depositaría</v>
+        <v>desapacible</v>
       </c>
       <c r="B262" t="str">
-        <v>tesouraría</v>
+        <v>desapracible</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>desapacible</v>
+        <v>desapromar</v>
       </c>
       <c r="B263" t="str">
-        <v>desapracible</v>
+        <v>desachumbar</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>desapromar</v>
+        <v>descalabro</v>
       </c>
       <c r="B264" t="str">
-        <v>desachumbar</v>
+        <v>desfeita</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>descalabro</v>
+        <v>descalificación</v>
       </c>
       <c r="B265" t="str">
-        <v>desfeita</v>
+        <v>descualificación</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>descalificación</v>
+        <v>descalificar</v>
       </c>
       <c r="B266" t="str">
-        <v>descualificación</v>
+        <v>descualificar</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>descalificar</v>
+        <v>descomenencia</v>
       </c>
       <c r="B267" t="str">
-        <v>descualificar</v>
+        <v>desconveniencia</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>descomenencia</v>
+        <v>desconxurar</v>
       </c>
       <c r="B268" t="str">
-        <v>desconveniencia</v>
+        <v>esconxurar</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>desconxurar</v>
+        <v>descubillar</v>
       </c>
       <c r="B269" t="str">
-        <v>esconxurar</v>
+        <v>desacubillar</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>descubillar</v>
+        <v>desembrullar</v>
       </c>
       <c r="B270" t="str">
-        <v>desacubillar</v>
+        <v>desenvurullar</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>desembrullar</v>
+        <v>desembrullo</v>
       </c>
       <c r="B271" t="str">
-        <v>desenvurullar</v>
+        <v>desenvurullo</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>desembrullo</v>
+        <v>desgracia</v>
       </c>
       <c r="B272" t="str">
-        <v>desenvurullo</v>
+        <v>desgraza</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>desgracia</v>
+        <v>deslizar</v>
       </c>
       <c r="B273" t="str">
-        <v>desgraza</v>
+        <v>escorregar</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>deslizar</v>
+        <v>deslumbrar</v>
       </c>
       <c r="B274" t="str">
-        <v>escorregar</v>
+        <v>cegar</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>deslumbrar</v>
+        <v>desmoronar</v>
       </c>
       <c r="B275" t="str">
-        <v>cegar</v>
+        <v>esborrallar</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>desmoronar</v>
+        <v>desnudar</v>
       </c>
       <c r="B276" t="str">
-        <v>esborrallar</v>
+        <v>despir</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>desnudar</v>
+        <v>despego</v>
       </c>
       <c r="B277" t="str">
-        <v>despir</v>
+        <v>desapego</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>despego</v>
+        <v>desprevenidamente</v>
       </c>
       <c r="B278" t="str">
-        <v>desapego</v>
+        <v>desprevidamente</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>desprevenidamente</v>
+        <v>destrozar</v>
       </c>
       <c r="B279" t="str">
-        <v>desprevidamente</v>
+        <v>esnaquizar</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>destrozar</v>
+        <v>desvaer</v>
       </c>
       <c r="B280" t="str">
-        <v>esnaquizar</v>
+        <v>esvaecer</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>desvaer</v>
+        <v>detentar</v>
       </c>
       <c r="B281" t="str">
-        <v>esvaecer</v>
+        <v>deter</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>detentar</v>
+        <v>devengar</v>
       </c>
       <c r="B282" t="str">
-        <v>deter</v>
+        <v>devindicar</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>devengar</v>
+        <v>devengo</v>
       </c>
       <c r="B283" t="str">
-        <v>devindicar</v>
+        <v>devindicación</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>devengo</v>
+        <v>diferencia</v>
       </c>
       <c r="B284" t="str">
-        <v>devindicación</v>
+        <v>diferenza</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>diferencia</v>
+        <v>disconforme</v>
       </c>
       <c r="B285" t="str">
-        <v>diferenza</v>
+        <v>desconforme</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>disconforme</v>
+        <v>discontinuidade</v>
       </c>
       <c r="B286" t="str">
-        <v>desconforme</v>
+        <v>descontinuidade</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>discontinuidade</v>
+        <v>discontinuo</v>
       </c>
       <c r="B287" t="str">
-        <v>descontinuidade</v>
+        <v>descontinuo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>discontinuo</v>
+        <v>disculpar</v>
       </c>
       <c r="B288" t="str">
-        <v>descontinuo</v>
+        <v>desculpar</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>disculpar</v>
+        <v>discurrir</v>
       </c>
       <c r="B289" t="str">
-        <v>desculpar</v>
+        <v>discorrer</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>discurrir</v>
+        <v>disfrutar</v>
       </c>
       <c r="B290" t="str">
-        <v>discorrer</v>
+        <v>gozar</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>disfrutar</v>
+        <v>disgustar</v>
       </c>
       <c r="B291" t="str">
-        <v>gozar</v>
+        <v>desgustar</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>disgustar</v>
+        <v>disgusto</v>
       </c>
       <c r="B292" t="str">
-        <v>desgustar</v>
+        <v>desgusto</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>disgusto</v>
+        <v>disminuír</v>
       </c>
       <c r="B293" t="str">
-        <v>desgusto</v>
+        <v>diminuír</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>disminuír</v>
+        <v>dóping</v>
       </c>
       <c r="B294" t="str">
-        <v>diminuír</v>
+        <v>dopaxe</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>dóping</v>
+        <v>eis</v>
       </c>
       <c r="B295" t="str">
-        <v>dopaxe</v>
+        <v>velaí</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>eis</v>
+        <v>elle</v>
       </c>
       <c r="B296" t="str">
-        <v>velaí</v>
+        <v>ele duplo</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>elle</v>
+        <v>elmo</v>
       </c>
       <c r="B297" t="str">
-        <v>ele duplo</v>
+        <v>helmo</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>elmo</v>
+        <v>embear</v>
       </c>
       <c r="B298" t="str">
-        <v>helmo</v>
+        <v>envear</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>embear</v>
+        <v>emborca</v>
       </c>
       <c r="B299" t="str">
-        <v>envear</v>
+        <v>envorca</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>emborca</v>
+        <v>emborcadura</v>
       </c>
       <c r="B300" t="str">
-        <v>envorca</v>
+        <v>envorcadura</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>emborcadura</v>
+        <v>emborcalladas</v>
       </c>
       <c r="B301" t="str">
-        <v>envorcadura</v>
+        <v>envorcalladas</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>emborcalladas</v>
+        <v>emborcallar</v>
       </c>
       <c r="B302" t="str">
-        <v>envorcalladas</v>
+        <v>envorcallar</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>emborcallar</v>
+        <v>emborcar</v>
       </c>
       <c r="B303" t="str">
-        <v>envorcallar</v>
+        <v>envorcar</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>emborcar</v>
+        <v>emborco</v>
       </c>
       <c r="B304" t="str">
-        <v>envorcar</v>
+        <v>envorco</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>emborco</v>
+        <v>embrullada</v>
       </c>
       <c r="B305" t="str">
-        <v>envorco</v>
+        <v>envurullada</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>embrullada</v>
+        <v>embrullar</v>
       </c>
       <c r="B306" t="str">
-        <v>envurullada</v>
+        <v>envurullar</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>embrullar</v>
+        <v>embrullo</v>
       </c>
       <c r="B307" t="str">
-        <v>envurullar</v>
+        <v>envurullo</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>embrullo</v>
+        <v>emburullada</v>
       </c>
       <c r="B308" t="str">
-        <v>envurullo</v>
+        <v>envurullada</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>emburullada</v>
+        <v>emburullar</v>
       </c>
       <c r="B309" t="str">
-        <v>envurullada</v>
+        <v>envurullar</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>emburullar</v>
+        <v>emburullo</v>
       </c>
       <c r="B310" t="str">
-        <v>envurullar</v>
+        <v>envurullo</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>emburullo</v>
+        <v>embuzar</v>
       </c>
       <c r="B311" t="str">
-        <v>envurullo</v>
+        <v>embozar</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>embuzar</v>
+        <v>embuzo</v>
       </c>
       <c r="B312" t="str">
-        <v>embozar</v>
+        <v>embozo</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>embuzo</v>
+        <v>empola</v>
       </c>
       <c r="B313" t="str">
-        <v>embozo</v>
+        <v>ampola</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>empola</v>
+        <v>enemigar</v>
       </c>
       <c r="B314" t="str">
-        <v>ampola</v>
+        <v>poñer a mal</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>enemigar</v>
+        <v>enfoscar</v>
       </c>
       <c r="B315" t="str">
-        <v>poñer a mal</v>
+        <v>enfuscar</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>enfoscar</v>
+        <v>enfrentamento</v>
       </c>
       <c r="B316" t="str">
-        <v>enfuscar</v>
+        <v>enfrontamento</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>enfrentamento</v>
+        <v>enfrentar</v>
       </c>
       <c r="B317" t="str">
-        <v>enfrontamento</v>
+        <v>enfrontar</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>enfrentar</v>
+        <v>enfriar</v>
       </c>
       <c r="B318" t="str">
-        <v>enfrontar</v>
+        <v>arrefriar</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>enfriar</v>
+        <v>engader</v>
       </c>
       <c r="B319" t="str">
-        <v>arrefriar</v>
+        <v>engadir</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>engader</v>
+        <v>engranar</v>
       </c>
       <c r="B320" t="str">
-        <v>engadir</v>
+        <v>engrenar</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>engranar</v>
+        <v>enmenda</v>
       </c>
       <c r="B321" t="str">
-        <v>engrenar</v>
+        <v>emenda</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>enmenda</v>
+        <v>enoxar</v>
       </c>
       <c r="B322" t="str">
-        <v>emenda</v>
+        <v>anoxar</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>enoxar</v>
+        <v>ensuxar</v>
       </c>
       <c r="B323" t="str">
-        <v>anoxar</v>
+        <v>ensuciar</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>ensuxar</v>
+        <v>entonces</v>
       </c>
       <c r="B324" t="str">
-        <v>ensuciar</v>
+        <v>entón</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>entonces</v>
+        <v>entrenar</v>
       </c>
       <c r="B325" t="str">
-        <v>entón</v>
+        <v>adestrar</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>entrenar</v>
+        <v>enxabroar</v>
       </c>
       <c r="B326" t="str">
-        <v>adestrar</v>
+        <v>enxaboar</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>enxabroar</v>
+        <v>equis</v>
       </c>
       <c r="B327" t="str">
-        <v>enxaboar</v>
+        <v>xe</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>equis</v>
+        <v>erogación</v>
       </c>
       <c r="B328" t="str">
-        <v>xe</v>
+        <v>errogación</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>erogación</v>
+        <v>erogar</v>
       </c>
       <c r="B329" t="str">
-        <v>errogación</v>
+        <v>errogar</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>erogar</v>
+        <v>escalón</v>
       </c>
       <c r="B330" t="str">
-        <v>errogar</v>
+        <v>chanzo</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>escalón</v>
+        <v>escalonar</v>
       </c>
       <c r="B331" t="str">
-        <v>chanzo</v>
+        <v>graduar</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>escalonar</v>
+        <v>espaciadamente</v>
       </c>
       <c r="B332" t="str">
-        <v>graduar</v>
+        <v>espazadamente</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>espaciadamente</v>
+        <v>espaciador</v>
       </c>
       <c r="B333" t="str">
-        <v>espazadamente</v>
+        <v>espazador</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>espaciador</v>
+        <v>espaciar</v>
       </c>
       <c r="B334" t="str">
-        <v>espazador</v>
+        <v>espazar</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>espaciar</v>
+        <v>espacio</v>
       </c>
       <c r="B335" t="str">
-        <v>espazar</v>
+        <v>espazo</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>espacio</v>
+        <v>espacioso</v>
       </c>
       <c r="B336" t="str">
-        <v>espazo</v>
+        <v>espazoso</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>espacioso</v>
+        <v>espaldeira</v>
       </c>
       <c r="B337" t="str">
-        <v>espazoso</v>
+        <v>espaleira</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>espaldeira</v>
+        <v>esperrear</v>
       </c>
       <c r="B338" t="str">
-        <v>espaleira</v>
+        <v>espirrar</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>esperrear</v>
+        <v>espulgar</v>
       </c>
       <c r="B339" t="str">
-        <v>espirrar</v>
+        <v>esburgar</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>espulgar</v>
+        <v>esquela</v>
       </c>
       <c r="B340" t="str">
-        <v>esburgar</v>
+        <v>necrolóxica</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>esquela</v>
+        <v>esquirol</v>
       </c>
       <c r="B341" t="str">
-        <v>necrolóxica</v>
+        <v>crebafolgas</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>esquirol</v>
+        <v>exacoraliarios</v>
       </c>
       <c r="B342" t="str">
-        <v>crebafolgas</v>
+        <v>hexacoraliarios</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>exacoraliarios</v>
+        <v>farra</v>
       </c>
       <c r="B343" t="str">
-        <v>hexacoraliarios</v>
+        <v>troula</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>farra</v>
+        <v>farrago</v>
       </c>
       <c r="B344" t="str">
-        <v>troula</v>
+        <v>fargallada</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>farrago</v>
+        <v>farún</v>
       </c>
       <c r="B345" t="str">
-        <v>fargallada</v>
+        <v>ferún</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>farún</v>
+        <v>faterna</v>
       </c>
       <c r="B346" t="str">
-        <v>ferún</v>
+        <v>fraterna</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>faterna</v>
+        <v>feed-back</v>
       </c>
       <c r="B347" t="str">
-        <v>fraterna</v>
+        <v>retroacción</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>feed-back</v>
+        <v>finca</v>
       </c>
       <c r="B348" t="str">
-        <v>retroacción</v>
+        <v>predio</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>finca</v>
+        <v>flota</v>
       </c>
       <c r="B349" t="str">
-        <v>predio</v>
+        <v>frota</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>flota</v>
+        <v>fornear</v>
       </c>
       <c r="B350" t="str">
-        <v>frota</v>
+        <v>enfornar</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>fornear</v>
+        <v>fornillo</v>
       </c>
       <c r="B351" t="str">
-        <v>enfornar</v>
+        <v>fornelo</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>fornillo</v>
+        <v>foulard</v>
       </c>
       <c r="B352" t="str">
-        <v>fornelo</v>
+        <v>fular</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>foulard</v>
+        <v>fragancia</v>
       </c>
       <c r="B353" t="str">
-        <v>fular</v>
+        <v>fragrancia</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>fragancia</v>
+        <v>franela</v>
       </c>
       <c r="B354" t="str">
-        <v>fragrancia</v>
+        <v>flanela</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>franela</v>
+        <v>frente</v>
       </c>
       <c r="B355" t="str">
-        <v>flanela</v>
+        <v>fronte</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>frente</v>
+        <v>fresa</v>
       </c>
       <c r="B356" t="str">
-        <v>fronte</v>
+        <v>amorodo</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>fresa</v>
+        <v>fuciño</v>
       </c>
       <c r="B357" t="str">
-        <v>amorodo</v>
+        <v>fociño</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>fuciño</v>
+        <v>fugar</v>
       </c>
       <c r="B358" t="str">
-        <v>fociño</v>
+        <v>fuxir</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>fugar</v>
+        <v>fumo</v>
       </c>
       <c r="B359" t="str">
-        <v>fuxir</v>
+        <v>fume</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>fumo</v>
+        <v>furruxe</v>
       </c>
       <c r="B360" t="str">
-        <v>fume</v>
+        <v>ferruxe</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>furruxe</v>
+        <v>gabacho</v>
       </c>
       <c r="B361" t="str">
-        <v>ferruxe</v>
+        <v>gavacho</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>gabacho</v>
+        <v>gábea</v>
       </c>
       <c r="B362" t="str">
-        <v>gavacho</v>
+        <v>gabia</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>gábea</v>
+        <v>gabela</v>
       </c>
       <c r="B363" t="str">
-        <v>gabia</v>
+        <v>gavela</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>gabela</v>
+        <v>gafas</v>
       </c>
       <c r="B364" t="str">
-        <v>gavela</v>
+        <v>lentes</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>gafas</v>
+        <v>gallope</v>
       </c>
       <c r="B365" t="str">
-        <v>lentes</v>
+        <v>galope</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>gallope</v>
+        <v>galpón</v>
       </c>
       <c r="B366" t="str">
-        <v>galope</v>
+        <v>pendello</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>galpón</v>
+        <v>ganchillo</v>
       </c>
       <c r="B367" t="str">
-        <v>pendello</v>
+        <v>gancho</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>ganchillo</v>
+        <v>gandra</v>
       </c>
       <c r="B368" t="str">
-        <v>gancho</v>
+        <v>gándara</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>gandra</v>
+        <v>ganés</v>
       </c>
       <c r="B369" t="str">
-        <v>gándara</v>
+        <v>ghanés</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>ganés</v>
+        <v>gañote</v>
       </c>
       <c r="B370" t="str">
-        <v>ghanés</v>
+        <v>garneato</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>gañote</v>
+        <v>garabanzo</v>
       </c>
       <c r="B371" t="str">
-        <v>garneato</v>
+        <v>garavanzo</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>garabanzo</v>
+        <v>garmalleira</v>
       </c>
       <c r="B372" t="str">
-        <v>garavanzo</v>
+        <v>gramalleira</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>garmalleira</v>
+        <v>gávea</v>
       </c>
       <c r="B373" t="str">
-        <v>gramalleira</v>
+        <v>gabia</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>gávea</v>
+        <v>gavear</v>
       </c>
       <c r="B374" t="str">
-        <v>gabia</v>
+        <v>gabear</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>gavear</v>
+        <v>gaveta</v>
       </c>
       <c r="B375" t="str">
-        <v>gabear</v>
+        <v>gabeta</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>gaveta</v>
+        <v>gavián</v>
       </c>
       <c r="B376" t="str">
-        <v>gabeta</v>
+        <v>gabián</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>gavián</v>
+        <v>gazapo</v>
       </c>
       <c r="B377" t="str">
-        <v>gabián</v>
+        <v>cazapo</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>gazapo</v>
+        <v>goldra</v>
       </c>
       <c r="B378" t="str">
-        <v>cazapo</v>
+        <v>bóldrega</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>goldra</v>
+        <v>golo</v>
       </c>
       <c r="B379" t="str">
-        <v>bóldrega</v>
+        <v>goro</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>golo</v>
+        <v>gomitar</v>
       </c>
       <c r="B380" t="str">
-        <v>goro</v>
+        <v>vomitar</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>gomitar</v>
+        <v>gorgullar</v>
       </c>
       <c r="B381" t="str">
-        <v>vomitar</v>
+        <v>gurgullar</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>gorgullar</v>
+        <v>grabar</v>
       </c>
       <c r="B382" t="str">
-        <v>gurgullar</v>
+        <v>gravar</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>grabar</v>
+        <v>grada</v>
       </c>
       <c r="B383" t="str">
-        <v>gravar</v>
+        <v>chanzo</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>grada</v>
+        <v>graderío</v>
       </c>
       <c r="B384" t="str">
-        <v>chanzo</v>
+        <v>bancada</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>graderío</v>
+        <v>granar</v>
       </c>
       <c r="B385" t="str">
-        <v>bancada</v>
+        <v>engraiar</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>granar</v>
+        <v>granicela</v>
       </c>
       <c r="B386" t="str">
-        <v>engraiar</v>
+        <v>gradicela</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>granicela</v>
+        <v>grao</v>
       </c>
       <c r="B387" t="str">
-        <v>gradicela</v>
+        <v>gran</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>grao</v>
+        <v>grasa</v>
       </c>
       <c r="B388" t="str">
-        <v>gran</v>
+        <v>graxa</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>grasa</v>
+        <v>grial</v>
       </c>
       <c r="B389" t="str">
-        <v>graxa</v>
+        <v>graal</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>grial</v>
+        <v>grifo</v>
       </c>
       <c r="B390" t="str">
-        <v>graal</v>
+        <v>billa</v>
       </c>
     </row>
     <row r="391">
@@ -12171,639 +12171,639 @@
         <v>grifo</v>
       </c>
       <c r="B391" t="str">
-        <v>billa</v>
+        <v>grifón</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>grifo</v>
+        <v>grinalda</v>
       </c>
       <c r="B392" t="str">
-        <v>grifón</v>
+        <v>grilanda</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>grinalda</v>
+        <v>grulla</v>
       </c>
       <c r="B393" t="str">
-        <v>grilanda</v>
+        <v>grúa</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>grulla</v>
+        <v>guarismo</v>
       </c>
       <c r="B394" t="str">
-        <v>grúa</v>
+        <v>algarismo</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>guarismo</v>
+        <v>gubernabilidade</v>
       </c>
       <c r="B395" t="str">
-        <v>algarismo</v>
+        <v>gobernabilidade</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>gubernabilidade</v>
+        <v>gubernamental</v>
       </c>
       <c r="B396" t="str">
-        <v>gobernabilidade</v>
+        <v>gobernamental</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>gubernamental</v>
+        <v>gueipo</v>
       </c>
       <c r="B397" t="str">
-        <v>gobernamental</v>
+        <v>queipo</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>gueipo</v>
+        <v>guirnalda</v>
       </c>
       <c r="B398" t="str">
-        <v>queipo</v>
+        <v>grilanda</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>guirnalda</v>
+        <v>harpa</v>
       </c>
       <c r="B399" t="str">
-        <v>grilanda</v>
+        <v>arpa</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>harpa</v>
+        <v>hashtag</v>
       </c>
       <c r="B400" t="str">
-        <v>arpa</v>
+        <v>cancelo</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>hashtag</v>
+        <v>hematí</v>
       </c>
       <c r="B401" t="str">
-        <v>cancelo</v>
+        <v>hemacia</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>hematí</v>
+        <v>hierarca</v>
       </c>
       <c r="B402" t="str">
-        <v>hemacia</v>
+        <v>xerarca</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>hierarca</v>
+        <v>hieróglifo</v>
       </c>
       <c r="B403" t="str">
-        <v>xerarca</v>
+        <v>xeróglifo</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>hieróglifo</v>
+        <v>hola</v>
       </c>
       <c r="B404" t="str">
-        <v>xeróglifo</v>
+        <v>ola</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>hola</v>
+        <v>hombro</v>
       </c>
       <c r="B405" t="str">
-        <v>ola</v>
+        <v>ombro</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>hombro</v>
+        <v>horchata</v>
       </c>
       <c r="B406" t="str">
-        <v>ombro</v>
+        <v>orchata</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>horchata</v>
+        <v>hornillo</v>
       </c>
       <c r="B407" t="str">
-        <v>orchata</v>
+        <v>fornelo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>hornillo</v>
+        <v>húmero</v>
       </c>
       <c r="B408" t="str">
-        <v>fornelo</v>
+        <v>úmero</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>húmero</v>
+        <v>humidal</v>
       </c>
       <c r="B409" t="str">
-        <v>úmero</v>
+        <v>zona húmida</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>humidal</v>
+        <v>icono</v>
       </c>
       <c r="B410" t="str">
-        <v>zona húmida</v>
+        <v>icona</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>icono</v>
+        <v>idoiro</v>
       </c>
       <c r="B411" t="str">
-        <v>icona</v>
+        <v>doiro</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>idoiro</v>
+        <v>igar</v>
       </c>
       <c r="B412" t="str">
-        <v>doiro</v>
+        <v>iguar</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>igar</v>
+        <v>iguala</v>
       </c>
       <c r="B413" t="str">
-        <v>iguar</v>
+        <v>avinza</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>iguala</v>
+        <v>il</v>
       </c>
       <c r="B414" t="str">
-        <v>avinza</v>
+        <v>el</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>il</v>
+        <v>imbar</v>
       </c>
       <c r="B415" t="str">
-        <v>el</v>
+        <v>enviar</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>imbar</v>
+        <v>impetigo</v>
       </c>
       <c r="B416" t="str">
-        <v>enviar</v>
+        <v>impetixe</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>impetigo</v>
+        <v>imponente</v>
       </c>
       <c r="B417" t="str">
-        <v>impetixe</v>
+        <v>impoñente</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>imponente</v>
+        <v>inantes</v>
       </c>
       <c r="B418" t="str">
-        <v>impoñente</v>
+        <v>iñantes</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>inantes</v>
+        <v>inasequible</v>
       </c>
       <c r="B419" t="str">
-        <v>iñantes</v>
+        <v>inaccesible</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>inasequible</v>
+        <v>inchenta</v>
       </c>
       <c r="B420" t="str">
-        <v>inaccesible</v>
+        <v>enchente</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>inchenta</v>
+        <v>incordio</v>
       </c>
       <c r="B421" t="str">
-        <v>enchente</v>
+        <v>encordio</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>incordio</v>
+        <v>indiferencia</v>
       </c>
       <c r="B422" t="str">
-        <v>encordio</v>
+        <v>indiferenza</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>indiferencia</v>
+        <v>inglete</v>
       </c>
       <c r="B423" t="str">
-        <v>indiferenza</v>
+        <v>bispel</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>inglete</v>
+        <v>insobornable</v>
       </c>
       <c r="B424" t="str">
-        <v>bispel</v>
+        <v>insubornable</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>insobornable</v>
+        <v>insumisión</v>
       </c>
       <c r="B425" t="str">
-        <v>insubornable</v>
+        <v>insubmisión</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>insumisión</v>
+        <v>interlínea</v>
       </c>
       <c r="B426" t="str">
-        <v>insubmisión</v>
+        <v>entreliña</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>interlínea</v>
+        <v>intertrigo</v>
       </c>
       <c r="B427" t="str">
-        <v>entreliña</v>
+        <v>intertrixe</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>intertrigo</v>
+        <v>intrincar</v>
       </c>
       <c r="B428" t="str">
-        <v>intertrixe</v>
+        <v>intricar</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>intrincar</v>
+        <v>inxenio</v>
       </c>
       <c r="B429" t="str">
-        <v>intricar</v>
+        <v>enxeño</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>inxenio</v>
+        <v>inxerir</v>
       </c>
       <c r="B430" t="str">
-        <v>enxeño</v>
+        <v>enxerir</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>inxerir</v>
+        <v>inxertar</v>
       </c>
       <c r="B431" t="str">
-        <v>enxerir</v>
+        <v>enxertar</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>inxertar</v>
+        <v>irremprazable</v>
       </c>
       <c r="B432" t="str">
-        <v>enxertar</v>
+        <v>insubstituíble</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>irremprazable</v>
+        <v>kermesse</v>
       </c>
       <c r="B433" t="str">
-        <v>insubstituíble</v>
+        <v>quermese</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>kermesse</v>
+        <v>laberinto</v>
       </c>
       <c r="B434" t="str">
-        <v>quermese</v>
+        <v>labirinto</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>laberinto</v>
+        <v>ladilla</v>
       </c>
       <c r="B435" t="str">
-        <v>labirinto</v>
+        <v>piollo pato</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>ladilla</v>
+        <v>lápiz</v>
       </c>
       <c r="B436" t="str">
-        <v>piollo pato</v>
+        <v>lapis</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>lápiz</v>
+        <v>lapón</v>
       </c>
       <c r="B437" t="str">
-        <v>lapis</v>
+        <v>saami</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>lapón</v>
+        <v>lentilla</v>
       </c>
       <c r="B438" t="str">
-        <v>saami</v>
+        <v>lente de contacto</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>lentilla</v>
+        <v>lexía</v>
       </c>
       <c r="B439" t="str">
-        <v>lente de contacto</v>
+        <v>lixivia</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>lexía</v>
+        <v>libreta</v>
       </c>
       <c r="B440" t="str">
-        <v>lixivia</v>
+        <v>caderno</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>libreta</v>
+        <v>licencia</v>
       </c>
       <c r="B441" t="str">
-        <v>caderno</v>
+        <v>licenza</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>licencia</v>
+        <v>limonada</v>
       </c>
       <c r="B442" t="str">
-        <v>licenza</v>
+        <v>limoada</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>limonada</v>
+        <v>linterna</v>
       </c>
       <c r="B443" t="str">
-        <v>limoada</v>
+        <v>lanterna</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>linterna</v>
+        <v>lío</v>
       </c>
       <c r="B444" t="str">
-        <v>lanterna</v>
+        <v>embrolla</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>lío</v>
+        <v>llerga</v>
       </c>
       <c r="B445" t="str">
-        <v>embrolla</v>
+        <v>legra</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>llerga</v>
+        <v>loro</v>
       </c>
       <c r="B446" t="str">
-        <v>legra</v>
+        <v>papagaio</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>loro</v>
+        <v>madastra</v>
       </c>
       <c r="B447" t="str">
-        <v>papagaio</v>
+        <v>madrasta</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>madastra</v>
+        <v>maiorazgo</v>
       </c>
       <c r="B448" t="str">
-        <v>madrasta</v>
+        <v>morgado</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>maiorazgo</v>
+        <v>maitíns</v>
       </c>
       <c r="B449" t="str">
-        <v>morgado</v>
+        <v>matinas</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>maitíns</v>
+        <v>malquerencia</v>
       </c>
       <c r="B450" t="str">
-        <v>matinas</v>
+        <v>malquerenza</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>malquerencia</v>
+        <v>manada</v>
       </c>
       <c r="B451" t="str">
-        <v>malquerenza</v>
+        <v>manda</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>manada</v>
+        <v>mango</v>
       </c>
       <c r="B452" t="str">
-        <v>manda</v>
+        <v>manga</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>mango</v>
+        <v>manillar</v>
       </c>
       <c r="B453" t="str">
-        <v>manga</v>
+        <v>guiador</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>manillar</v>
+        <v>maniobra</v>
       </c>
       <c r="B454" t="str">
-        <v>guiador</v>
+        <v>manobra</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>maniobra</v>
+        <v>manosear</v>
       </c>
       <c r="B455" t="str">
-        <v>manobra</v>
+        <v>apalpar</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>manosear</v>
+        <v>manzanilla</v>
       </c>
       <c r="B456" t="str">
-        <v>apalpar</v>
+        <v>macela</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>manzanilla</v>
+        <v>marafallada</v>
       </c>
       <c r="B457" t="str">
-        <v>macela</v>
+        <v>marfallada</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>marafallada</v>
+        <v>maravedí</v>
       </c>
       <c r="B458" t="str">
-        <v>marfallada</v>
+        <v>marabedí</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>maravedí</v>
+        <v>maravilla</v>
       </c>
       <c r="B459" t="str">
-        <v>marabedí</v>
+        <v>marabilla</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>maravilla</v>
+        <v>maravillosamente</v>
       </c>
       <c r="B460" t="str">
-        <v>marabilla</v>
+        <v>marabillosamente</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>maravillosamente</v>
+        <v>mariguana</v>
       </c>
       <c r="B461" t="str">
-        <v>marabillosamente</v>
+        <v>marihuana</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>mariguana</v>
+        <v>mariposa</v>
       </c>
       <c r="B462" t="str">
-        <v>marihuana</v>
+        <v>bolboreta</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>mariposa</v>
+        <v>martín pescador</v>
       </c>
       <c r="B463" t="str">
-        <v>bolboreta</v>
+        <v>martiño peixeiro</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>martín pescador</v>
+        <v>mástil</v>
       </c>
       <c r="B464" t="str">
-        <v>martiño peixeiro</v>
+        <v>mastro</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>mástil</v>
+        <v>mazmorra</v>
       </c>
       <c r="B465" t="str">
-        <v>mastro</v>
+        <v>alxube</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>mazmorra</v>
+        <v>mecer</v>
       </c>
       <c r="B466" t="str">
-        <v>alxube</v>
+        <v>mexer</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>mecer</v>
+        <v>meixarigo</v>
       </c>
       <c r="B467" t="str">
-        <v>mexer</v>
+        <v>neixarigo</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>meixarigo</v>
+        <v>menchevique</v>
       </c>
       <c r="B468" t="str">
-        <v>neixarigo</v>
+        <v>menxevique</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>menchevique</v>
+        <v>menestra</v>
       </c>
       <c r="B469" t="str">
-        <v>menxevique</v>
+        <v>minestra</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>menestra</v>
+        <v>merino</v>
       </c>
       <c r="B470" t="str">
-        <v>minestra</v>
+        <v>meiriño</v>
       </c>
     </row>
     <row r="471">
@@ -12816,90 +12816,90 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>merino</v>
+        <v>mermar</v>
       </c>
       <c r="B472" t="str">
-        <v>meiriño</v>
+        <v>minguar</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>mermar</v>
+        <v>meruxa</v>
       </c>
       <c r="B473" t="str">
-        <v>minguar</v>
+        <v>muruxa</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>meruxa</v>
+        <v>mezquita</v>
       </c>
       <c r="B474" t="str">
-        <v>muruxa</v>
+        <v>mesquita</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>mezquita</v>
+        <v>micra</v>
       </c>
       <c r="B475" t="str">
-        <v>mesquita</v>
+        <v>micrómetro</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>micra</v>
+        <v>milano</v>
       </c>
       <c r="B476" t="str">
-        <v>micrómetro</v>
+        <v>miñato</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>milano</v>
+        <v>miligacha</v>
       </c>
       <c r="B477" t="str">
-        <v>miñato</v>
+        <v>limacha</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>miligacha</v>
+        <v>millor</v>
       </c>
       <c r="B478" t="str">
-        <v>limacha</v>
+        <v>mellor</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>millor</v>
+        <v>milpéndora</v>
       </c>
       <c r="B479" t="str">
-        <v>mellor</v>
+        <v>ouriolo</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>milpéndora</v>
+        <v>minguilete</v>
       </c>
       <c r="B480" t="str">
-        <v>ouriolo</v>
+        <v>binguelete</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>minguilete</v>
+        <v>minuteiro</v>
       </c>
       <c r="B481" t="str">
-        <v>binguelete</v>
+        <v>agulla dos minutos</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>minuteiro</v>
+        <v>mirilla</v>
       </c>
       <c r="B482" t="str">
-        <v>agulla dos minutos</v>
+        <v>míllara</v>
       </c>
     </row>
     <row r="483">
@@ -12907,596 +12907,596 @@
         <v>mirilla</v>
       </c>
       <c r="B483" t="str">
-        <v>míllara</v>
+        <v>mira</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>mirilla</v>
+        <v>miruxa</v>
       </c>
       <c r="B484" t="str">
-        <v>mira</v>
+        <v>muruxa</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>miruxa</v>
+        <v>mitade</v>
       </c>
       <c r="B485" t="str">
-        <v>muruxa</v>
+        <v>metade</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>mitade</v>
+        <v>mixiricar</v>
       </c>
       <c r="B486" t="str">
-        <v>metade</v>
+        <v>mexericar</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>mixiricar</v>
+        <v>mocarte</v>
       </c>
       <c r="B487" t="str">
-        <v>mexericar</v>
+        <v>bocarte</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>mocarte</v>
+        <v>modelado</v>
       </c>
       <c r="B488" t="str">
-        <v>bocarte</v>
+        <v>modelaxe</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>modelado</v>
+        <v>modo, a</v>
       </c>
       <c r="B489" t="str">
-        <v>modelaxe</v>
+        <v>amodo</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>modo, a</v>
+        <v>mole</v>
       </c>
       <c r="B490" t="str">
-        <v>amodo</v>
+        <v>mol</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>mole</v>
+        <v>morango</v>
       </c>
       <c r="B491" t="str">
-        <v>mol</v>
+        <v>amorodo</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>morango</v>
+        <v>mordiscar</v>
       </c>
       <c r="B492" t="str">
-        <v>amorodo</v>
+        <v>adentar</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>mordiscar</v>
+        <v>mordisco</v>
       </c>
       <c r="B493" t="str">
-        <v>adentar</v>
+        <v>dentada</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>mordisco</v>
+        <v>morillo</v>
       </c>
       <c r="B494" t="str">
-        <v>dentada</v>
+        <v>trasfogueiro</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>morillo</v>
+        <v>mote</v>
       </c>
       <c r="B495" t="str">
-        <v>trasfogueiro</v>
+        <v>alcume</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>mote</v>
+        <v>mulo</v>
       </c>
       <c r="B496" t="str">
-        <v>alcume</v>
+        <v>macho</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>mulo</v>
+        <v>murriñada</v>
       </c>
       <c r="B497" t="str">
-        <v>macho</v>
+        <v>morriñada</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>murriñada</v>
+        <v>nacencia</v>
       </c>
       <c r="B498" t="str">
-        <v>morriñada</v>
+        <v>nacenza</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>nacencia</v>
+        <v>natilla</v>
       </c>
       <c r="B499" t="str">
-        <v>nacenza</v>
+        <v>crema</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>natilla</v>
+        <v>naxarigo</v>
       </c>
       <c r="B500" t="str">
-        <v>crema</v>
+        <v>neixarigo</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>naxarigo</v>
+        <v>negrillo</v>
       </c>
       <c r="B501" t="str">
-        <v>neixarigo</v>
+        <v>chopo negro</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>negrillo</v>
+        <v>negrita</v>
       </c>
       <c r="B502" t="str">
-        <v>chopo negro</v>
+        <v>grosa</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>negrita</v>
+        <v>neumático</v>
       </c>
       <c r="B503" t="str">
-        <v>grosa</v>
+        <v>pneumático</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>neumático</v>
+        <v>neumo-</v>
       </c>
       <c r="B504" t="str">
-        <v>pneumático</v>
+        <v>pneumo-</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>neumo-</v>
+        <v>neumonía</v>
       </c>
       <c r="B505" t="str">
-        <v>pneumo-</v>
+        <v>pneumonía</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>neumonía</v>
+        <v>néveda</v>
       </c>
       <c r="B506" t="str">
-        <v>pneumonía</v>
+        <v>nébeda</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>néveda</v>
+        <v>niqui</v>
       </c>
       <c r="B507" t="str">
-        <v>nébeda</v>
+        <v>polo</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>niqui</v>
+        <v>noraboa</v>
       </c>
       <c r="B508" t="str">
-        <v>polo</v>
+        <v>parabén</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>noraboa</v>
+        <v>obertura</v>
       </c>
       <c r="B509" t="str">
-        <v>parabén</v>
+        <v>abertura</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>obertura</v>
+        <v>obispo</v>
       </c>
       <c r="B510" t="str">
-        <v>abertura</v>
+        <v>bispo</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>obispo</v>
+        <v>obscuro</v>
       </c>
       <c r="B511" t="str">
-        <v>bispo</v>
+        <v>escuro</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>obscuro</v>
+        <v>oca</v>
       </c>
       <c r="B512" t="str">
-        <v>escuro</v>
+        <v>ganso</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>oca</v>
+        <v>odometría</v>
       </c>
       <c r="B513" t="str">
-        <v>ganso</v>
+        <v>hodometría</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>odometría</v>
+        <v>odómetro</v>
       </c>
       <c r="B514" t="str">
-        <v>hodometría</v>
+        <v>hodómetro</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>odómetro</v>
+        <v>oler</v>
       </c>
       <c r="B515" t="str">
-        <v>hodómetro</v>
+        <v>ulir</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>oler</v>
+        <v>olvidar</v>
       </c>
       <c r="B516" t="str">
-        <v>ulir</v>
+        <v>esquecer</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>olvidar</v>
+        <v>olvido</v>
       </c>
       <c r="B517" t="str">
-        <v>esquecer</v>
+        <v>esquecemento</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>olvido</v>
+        <v>orina</v>
       </c>
       <c r="B518" t="str">
-        <v>esquecemento</v>
+        <v>urina</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>orina</v>
+        <v>orquesta</v>
       </c>
       <c r="B519" t="str">
-        <v>urina</v>
+        <v>orquestra</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>orquesta</v>
+        <v>ourilucente</v>
       </c>
       <c r="B520" t="str">
-        <v>orquestra</v>
+        <v>aurilucente</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>ourilucente</v>
+        <v>padastro</v>
       </c>
       <c r="B521" t="str">
-        <v>aurilucente</v>
+        <v>padrasto</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>padastro</v>
+        <v>pagaré</v>
       </c>
       <c r="B522" t="str">
-        <v>padrasto</v>
+        <v>nota promisoria</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>pagaré</v>
+        <v>palanca</v>
       </c>
       <c r="B523" t="str">
-        <v>nota promisoria</v>
+        <v>panca</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>palanca</v>
+        <v>palear</v>
       </c>
       <c r="B524" t="str">
-        <v>panca</v>
+        <v>padexar</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>palear</v>
+        <v>palista</v>
       </c>
       <c r="B525" t="str">
-        <v>padexar</v>
+        <v>padexeiro</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>palista</v>
+        <v>pao</v>
       </c>
       <c r="B526" t="str">
-        <v>padexeiro</v>
+        <v>pau</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>pao</v>
+        <v>paolo</v>
       </c>
       <c r="B527" t="str">
-        <v>pau</v>
+        <v>paiolo</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>paolo</v>
+        <v>párrafo</v>
       </c>
       <c r="B528" t="str">
-        <v>paiolo</v>
+        <v>parágrafo</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>párrafo</v>
+        <v>patronato</v>
       </c>
       <c r="B529" t="str">
-        <v>parágrafo</v>
+        <v>padroado</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>patronato</v>
+        <v>peatón</v>
       </c>
       <c r="B530" t="str">
-        <v>padroado</v>
+        <v>peón</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>peatón</v>
+        <v>pechina</v>
       </c>
       <c r="B531" t="str">
-        <v>peón</v>
+        <v>pendente</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>pechina</v>
+        <v>penas, a</v>
       </c>
       <c r="B532" t="str">
-        <v>pendente</v>
+        <v>apenas</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>penas, a</v>
+        <v>pepino</v>
       </c>
       <c r="B533" t="str">
-        <v>apenas</v>
+        <v>cogombro</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>pepino</v>
+        <v>percutor</v>
       </c>
       <c r="B534" t="str">
-        <v>cogombro</v>
+        <v>percusor</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>percutor</v>
+        <v>perxudicar</v>
       </c>
       <c r="B535" t="str">
-        <v>percusor</v>
+        <v>danar</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>perxudicar</v>
+        <v>perxudicial</v>
       </c>
       <c r="B536" t="str">
-        <v>danar</v>
+        <v>prexudicial</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>perxudicial</v>
+        <v>perxuízo</v>
       </c>
       <c r="B537" t="str">
-        <v>prexudicial</v>
+        <v>prexuízo</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>perxuízo</v>
+        <v>pilar</v>
       </c>
       <c r="B538" t="str">
-        <v>prexuízo</v>
+        <v>piar</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>pilar</v>
+        <v>píldora</v>
       </c>
       <c r="B539" t="str">
-        <v>piar</v>
+        <v>pílula</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>píldora</v>
+        <v>pilón</v>
       </c>
       <c r="B540" t="str">
-        <v>pílula</v>
+        <v>pío</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>pilón</v>
+        <v>pimento</v>
       </c>
       <c r="B541" t="str">
-        <v>pío</v>
+        <v>pemento</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>pimento</v>
+        <v>pinzón</v>
       </c>
       <c r="B542" t="str">
-        <v>pemento</v>
+        <v>pimpín</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>pinzón</v>
+        <v>pirlón</v>
       </c>
       <c r="B543" t="str">
-        <v>pimpín</v>
+        <v>porlón</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>pirlón</v>
+        <v>pisapapeis</v>
       </c>
       <c r="B544" t="str">
-        <v>porlón</v>
+        <v>calcapapeis</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>pisapapeis</v>
+        <v>pitorro</v>
       </c>
       <c r="B545" t="str">
-        <v>calcapapeis</v>
+        <v>biquela</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>pitorro</v>
+        <v>pizarra</v>
       </c>
       <c r="B546" t="str">
-        <v>biquela</v>
+        <v>lousa</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>pizarra</v>
+        <v>plaga</v>
       </c>
       <c r="B547" t="str">
-        <v>lousa</v>
+        <v>praga</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>plaga</v>
+        <v>plancha</v>
       </c>
       <c r="B548" t="str">
-        <v>praga</v>
+        <v>ferro de pasar</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>plancha</v>
+        <v>planchar</v>
       </c>
       <c r="B549" t="str">
-        <v>ferro de pasar</v>
+        <v>pasar o ferro</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>planchar</v>
+        <v>plantilla do zapato</v>
       </c>
       <c r="B550" t="str">
-        <v>pasar o ferro</v>
+        <v>soleta do zapato</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>plantilla do zapato</v>
+        <v>playback</v>
       </c>
       <c r="B551" t="str">
-        <v>soleta do zapato</v>
+        <v>son pregravado</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>playback</v>
+        <v>pleistoceno</v>
       </c>
       <c r="B552" t="str">
-        <v>son pregravado</v>
+        <v>plistoceno</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>pleistoceno</v>
+        <v>pleito</v>
       </c>
       <c r="B553" t="str">
-        <v>plistoceno</v>
+        <v>preito</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>pleito</v>
+        <v>plumón</v>
       </c>
       <c r="B554" t="str">
-        <v>preito</v>
+        <v>penuxe</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>plumón</v>
+        <v>poa</v>
       </c>
       <c r="B555" t="str">
-        <v>penuxe</v>
+        <v>poia</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>poa</v>
+        <v>pócema</v>
       </c>
       <c r="B556" t="str">
-        <v>poia</v>
+        <v>apócema</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>pócema</v>
+        <v>pócima</v>
       </c>
       <c r="B557" t="str">
         <v>apócema</v>
@@ -13504,351 +13504,351 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>pócima</v>
+        <v>poia</v>
       </c>
       <c r="B558" t="str">
-        <v>apócema</v>
+        <v>poxa</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>poia</v>
+        <v>polichinela</v>
       </c>
       <c r="B559" t="str">
-        <v>poxa</v>
+        <v>pulchinelo</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>polichinela</v>
+        <v>polizón</v>
       </c>
       <c r="B560" t="str">
-        <v>pulchinelo</v>
+        <v>polisón</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>polizón</v>
+        <v>polrón</v>
       </c>
       <c r="B561" t="str">
-        <v>polisón</v>
+        <v>porlón</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>polrón</v>
+        <v>ponencia</v>
       </c>
       <c r="B562" t="str">
-        <v>porlón</v>
+        <v>relatorio</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>ponencia</v>
+        <v>ponente</v>
       </c>
       <c r="B563" t="str">
-        <v>relatorio</v>
+        <v>relator</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>ponente</v>
+        <v>porche</v>
       </c>
       <c r="B564" t="str">
-        <v>relator</v>
+        <v>soportal</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>porche</v>
+        <v>postema</v>
       </c>
       <c r="B565" t="str">
-        <v>soportal</v>
+        <v>apostema</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>postema</v>
+        <v>postrar</v>
       </c>
       <c r="B566" t="str">
-        <v>apostema</v>
+        <v>prostrar</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>postrar</v>
+        <v>postre</v>
       </c>
       <c r="B567" t="str">
-        <v>prostrar</v>
+        <v>sobremesa</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>postre</v>
+        <v>pranchar</v>
       </c>
       <c r="B568" t="str">
-        <v>sobremesa</v>
+        <v>pasar o ferro</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>pranchar</v>
+        <v>precio</v>
       </c>
       <c r="B569" t="str">
-        <v>pasar o ferro</v>
+        <v>prezo</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>precio</v>
+        <v>preconcebido</v>
       </c>
       <c r="B570" t="str">
-        <v>prezo</v>
+        <v>preconcibido</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>preconcebido</v>
+        <v>presencia</v>
       </c>
       <c r="B571" t="str">
-        <v>preconcibido</v>
+        <v>presenza</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>presencia</v>
+        <v>pro</v>
       </c>
       <c r="B572" t="str">
-        <v>presenza</v>
+        <v>prol</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>pro</v>
+        <v>proel</v>
       </c>
       <c r="B573" t="str">
-        <v>prol</v>
+        <v>proeiro</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>proel</v>
+        <v>prohome</v>
       </c>
       <c r="B574" t="str">
-        <v>proeiro</v>
+        <v>home de prol</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>prohome</v>
+        <v>promedio</v>
       </c>
       <c r="B575" t="str">
-        <v>home de prol</v>
+        <v>medio</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>promedio</v>
+        <v>pronóstico</v>
       </c>
       <c r="B576" t="str">
-        <v>medio</v>
+        <v>prognóstico</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>pronóstico</v>
+        <v>prorratear</v>
       </c>
       <c r="B577" t="str">
-        <v>prognóstico</v>
+        <v>ratear</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>prorratear</v>
+        <v>pulpo</v>
       </c>
       <c r="B578" t="str">
-        <v>ratear</v>
+        <v>polbo</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>pulpo</v>
+        <v>purín</v>
       </c>
       <c r="B579" t="str">
-        <v>polbo</v>
+        <v>xurro</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>purín</v>
+        <v>queila</v>
       </c>
       <c r="B580" t="str">
-        <v>xurro</v>
+        <v>queira</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>queila</v>
+        <v>queixoto</v>
       </c>
       <c r="B581" t="str">
-        <v>queira</v>
+        <v>coxote</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>queixoto</v>
+        <v>rábano</v>
       </c>
       <c r="B582" t="str">
-        <v>coxote</v>
+        <v>ravo</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>rábano</v>
+        <v>racha</v>
       </c>
       <c r="B583" t="str">
-        <v>ravo</v>
+        <v>refacho</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>racha</v>
+        <v>racimo</v>
       </c>
       <c r="B584" t="str">
-        <v>refacho</v>
+        <v>acio</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>racimo</v>
+        <v>ranura</v>
       </c>
       <c r="B585" t="str">
-        <v>acio</v>
+        <v>rañura</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ranura</v>
+        <v>rape</v>
       </c>
       <c r="B586" t="str">
-        <v>rañura</v>
+        <v>peixe sapo</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>rape</v>
+        <v>rapé</v>
       </c>
       <c r="B587" t="str">
-        <v>peixe sapo</v>
+        <v>repé</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>rapé</v>
+        <v>rapsoda</v>
       </c>
       <c r="B588" t="str">
-        <v>repé</v>
+        <v>rapsodo</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>rapsoda</v>
+        <v>raquis</v>
       </c>
       <c r="B589" t="str">
-        <v>rapsodo</v>
+        <v>raque</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>raquis</v>
+        <v>raseiro</v>
       </c>
       <c r="B590" t="str">
-        <v>raque</v>
+        <v>rapadoira</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>raseiro</v>
+        <v>rasgo</v>
       </c>
       <c r="B591" t="str">
-        <v>rapadoira</v>
+        <v>risco</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>rasgo</v>
+        <v>raso</v>
       </c>
       <c r="B592" t="str">
-        <v>risco</v>
+        <v>satén</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>raso</v>
+        <v>realengo</v>
       </c>
       <c r="B593" t="str">
-        <v>satén</v>
+        <v>reguengo</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>realengo</v>
+        <v>rebaño</v>
       </c>
       <c r="B594" t="str">
-        <v>reguengo</v>
+        <v>rabaño</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>rebaño</v>
+        <v>reboldá</v>
       </c>
       <c r="B595" t="str">
-        <v>rabaño</v>
+        <v>rebordá</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>reboldá</v>
+        <v>recelo</v>
       </c>
       <c r="B596" t="str">
-        <v>rebordá</v>
+        <v>roxelo</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>recelo</v>
+        <v>receso</v>
       </c>
       <c r="B597" t="str">
-        <v>roxelo</v>
+        <v>reseso</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>receso</v>
+        <v>rechear</v>
       </c>
       <c r="B598" t="str">
-        <v>reseso</v>
+        <v>reencher</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>rechear</v>
+        <v>recluta</v>
       </c>
       <c r="B599" t="str">
-        <v>reencher</v>
+        <v>recruta</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>recluta</v>
+        <v>recrudecer</v>
       </c>
       <c r="B600" t="str">
-        <v>recruta</v>
+        <v>recruar</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>recrudecer</v>
+        <v>recrudescer</v>
       </c>
       <c r="B601" t="str">
         <v>recruar</v>
@@ -13856,367 +13856,367 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>recrudescer</v>
+        <v>reemprazar</v>
       </c>
       <c r="B602" t="str">
-        <v>recruar</v>
+        <v>substituír</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>reemprazar</v>
+        <v>reflexar</v>
       </c>
       <c r="B603" t="str">
-        <v>substituír</v>
+        <v>reflectir</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>reflexar</v>
+        <v>refol</v>
       </c>
       <c r="B604" t="str">
-        <v>reflectir</v>
+        <v>redefol</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>refol</v>
+        <v>refriado</v>
       </c>
       <c r="B605" t="str">
-        <v>redefol</v>
+        <v>arrefriado</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>refriado</v>
+        <v>refriar</v>
       </c>
       <c r="B606" t="str">
-        <v>arrefriado</v>
+        <v>arrefriar</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>refriar</v>
+        <v>regaliz</v>
       </c>
       <c r="B607" t="str">
-        <v>arrefriar</v>
+        <v>regalicia</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>regaliz</v>
+        <v>regandixa</v>
       </c>
       <c r="B608" t="str">
-        <v>regalicia</v>
+        <v>fenda</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>regandixa</v>
+        <v>reigada</v>
       </c>
       <c r="B609" t="str">
-        <v>fenda</v>
+        <v>raigada</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>reigada</v>
+        <v>reigaña</v>
       </c>
       <c r="B610" t="str">
-        <v>raigada</v>
+        <v>raigaña</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>reigaña</v>
+        <v>remite</v>
       </c>
       <c r="B611" t="str">
-        <v>raigaña</v>
+        <v>remitente</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>remite</v>
+        <v>renacencia</v>
       </c>
       <c r="B612" t="str">
-        <v>remitente</v>
+        <v>renacenza</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>renacencia</v>
+        <v>reollo, de</v>
       </c>
       <c r="B613" t="str">
-        <v>renacenza</v>
+        <v>de esguello</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>reollo, de</v>
+        <v>reptil</v>
       </c>
       <c r="B614" t="str">
-        <v>de esguello</v>
+        <v>réptil</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>reptil</v>
+        <v>resfriado</v>
       </c>
       <c r="B615" t="str">
-        <v>réptil</v>
+        <v>arrefriado</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>resfriado</v>
+        <v>resfriar</v>
       </c>
       <c r="B616" t="str">
-        <v>arrefriado</v>
+        <v>arrefriar</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>resfriar</v>
+        <v>retrasar</v>
       </c>
       <c r="B617" t="str">
-        <v>arrefriar</v>
+        <v>atrasar</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>retrasar</v>
+        <v>revancha</v>
       </c>
       <c r="B618" t="str">
-        <v>atrasar</v>
+        <v>desquite</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>revancha</v>
+        <v>revoldaina</v>
       </c>
       <c r="B619" t="str">
-        <v>desquite</v>
+        <v>rebuldaina</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>revoldaina</v>
+        <v>ribete</v>
       </c>
       <c r="B620" t="str">
-        <v>rebuldaina</v>
+        <v>reberete</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ribete</v>
+        <v>rincón</v>
       </c>
       <c r="B621" t="str">
-        <v>reberete</v>
+        <v>canto</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>rincón</v>
+        <v>riñoneira</v>
       </c>
       <c r="B622" t="str">
-        <v>canto</v>
+        <v>alxibeira</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>riñoneira</v>
+        <v>rocío</v>
       </c>
       <c r="B623" t="str">
-        <v>alxibeira</v>
+        <v>rosada</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>rocío</v>
+        <v>ronco</v>
       </c>
       <c r="B624" t="str">
-        <v>rosada</v>
+        <v>rouco</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>ronco</v>
+        <v>ronqueira</v>
       </c>
       <c r="B625" t="str">
-        <v>rouco</v>
+        <v>rouquén</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>ronqueira</v>
+        <v>sabañón</v>
       </c>
       <c r="B626" t="str">
-        <v>rouquén</v>
+        <v>frieira</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>sabañón</v>
+        <v>sable</v>
       </c>
       <c r="B627" t="str">
-        <v>frieira</v>
+        <v>sabre</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>sable</v>
+        <v>savia</v>
       </c>
       <c r="B628" t="str">
-        <v>sabre</v>
+        <v>zume</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>savia</v>
+        <v>seba</v>
       </c>
       <c r="B629" t="str">
-        <v>zume</v>
+        <v>ceba</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>seba</v>
+        <v>secano</v>
       </c>
       <c r="B630" t="str">
-        <v>ceba</v>
+        <v>secaño</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>secano</v>
+        <v>secta</v>
       </c>
       <c r="B631" t="str">
-        <v>secaño</v>
+        <v>seita</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>secta</v>
+        <v>seglar</v>
       </c>
       <c r="B632" t="str">
-        <v>seita</v>
+        <v>segrar</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>seglar</v>
+        <v>seguida, de</v>
       </c>
       <c r="B633" t="str">
-        <v>segrar</v>
+        <v>deseguida</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>seguida, de</v>
+        <v>seguida, en</v>
       </c>
       <c r="B634" t="str">
-        <v>deseguida</v>
+        <v>enseguida</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>seguida, en</v>
+        <v>seguido, de</v>
       </c>
       <c r="B635" t="str">
-        <v>enseguida</v>
+        <v>deseguido</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>seguido, de</v>
+        <v>seísmo</v>
       </c>
       <c r="B636" t="str">
-        <v>deseguido</v>
+        <v>sismo</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>seísmo</v>
+        <v>sentencia</v>
       </c>
       <c r="B637" t="str">
-        <v>sismo</v>
+        <v>sentenza</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>sentencia</v>
+        <v>serrín</v>
       </c>
       <c r="B638" t="str">
-        <v>sentenza</v>
+        <v>serraduras</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>serrín</v>
+        <v>serro</v>
       </c>
       <c r="B639" t="str">
-        <v>serraduras</v>
+        <v>cerro</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>serro</v>
+        <v>servicial</v>
       </c>
       <c r="B640" t="str">
-        <v>cerro</v>
+        <v>servizal</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>servicial</v>
+        <v>servicio</v>
       </c>
       <c r="B641" t="str">
-        <v>servizal</v>
+        <v>servizo</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>servicio</v>
+        <v>servilleta</v>
       </c>
       <c r="B642" t="str">
-        <v>servizo</v>
+        <v>pano de mesa</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>servilleta</v>
+        <v>seta</v>
       </c>
       <c r="B643" t="str">
-        <v>pano de mesa</v>
+        <v>cogomelo</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>seta</v>
+        <v>silla</v>
       </c>
       <c r="B644" t="str">
-        <v>cogomelo</v>
+        <v>cadeira</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>silla</v>
+        <v>sillar</v>
       </c>
       <c r="B645" t="str">
-        <v>cadeira</v>
+        <v>perpiaño</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>sillar</v>
+        <v>sillaría</v>
       </c>
       <c r="B646" t="str">
-        <v>perpiaño</v>
+        <v>cadeirado</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>sillaría</v>
+        <v>sillería</v>
       </c>
       <c r="B647" t="str">
         <v>cadeirado</v>
@@ -14224,514 +14224,514 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>sillería</v>
+        <v>sillón</v>
       </c>
       <c r="B648" t="str">
-        <v>cadeirado</v>
+        <v>poltrona</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sillón</v>
+        <v>sintoísmo</v>
       </c>
       <c r="B649" t="str">
-        <v>poltrona</v>
+        <v>xintoísmo</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>sintoísmo</v>
+        <v>sipela</v>
       </c>
       <c r="B650" t="str">
-        <v>xintoísmo</v>
+        <v>erisipela</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>sipela</v>
+        <v>sisa</v>
       </c>
       <c r="B651" t="str">
-        <v>erisipela</v>
+        <v>escave</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>sisa</v>
+        <v>sobornar</v>
       </c>
       <c r="B652" t="str">
-        <v>escave</v>
+        <v>subornar</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>sobornar</v>
+        <v>socarronería</v>
       </c>
       <c r="B653" t="str">
-        <v>subornar</v>
+        <v>retranca</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>socarronería</v>
+        <v>sofocar</v>
       </c>
       <c r="B654" t="str">
-        <v>retranca</v>
+        <v>sufocar</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>sofocar</v>
+        <v>sonido</v>
       </c>
       <c r="B655" t="str">
-        <v>sufocar</v>
+        <v>son</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>sonido</v>
+        <v>sostenido</v>
       </c>
       <c r="B656" t="str">
-        <v>son</v>
+        <v>díese</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sostenido</v>
+        <v>stress</v>
       </c>
       <c r="B657" t="str">
-        <v>díese</v>
+        <v>estrés</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>stress</v>
+        <v>subasta</v>
       </c>
       <c r="B658" t="str">
-        <v>estrés</v>
+        <v>poxa</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>subasta</v>
+        <v>subastar</v>
       </c>
       <c r="B659" t="str">
-        <v>poxa</v>
+        <v>poxar</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>subastar</v>
+        <v>subministro</v>
       </c>
       <c r="B660" t="str">
-        <v>poxar</v>
+        <v>subministración</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>subministro</v>
+        <v>substraer</v>
       </c>
       <c r="B661" t="str">
-        <v>subministración</v>
+        <v>subtraer</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>substraer</v>
+        <v>sumerxir</v>
       </c>
       <c r="B662" t="str">
-        <v>subtraer</v>
+        <v>somerxer</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>sumerxir</v>
+        <v>suministrar</v>
       </c>
       <c r="B663" t="str">
-        <v>somerxer</v>
+        <v>subministrar</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>suministrar</v>
+        <v>suscribir</v>
       </c>
       <c r="B664" t="str">
-        <v>subministrar</v>
+        <v>subscribir</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>suscribir</v>
+        <v>suscrición</v>
       </c>
       <c r="B665" t="str">
-        <v>subscribir</v>
+        <v>subscrición</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>suscrición</v>
+        <v>suxerencia</v>
       </c>
       <c r="B666" t="str">
-        <v>subscrición</v>
+        <v>suxestión</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>suxerencia</v>
+        <v>taba</v>
       </c>
       <c r="B667" t="str">
-        <v>suxestión</v>
+        <v>chuca</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>taba</v>
+        <v>taburete</v>
       </c>
       <c r="B668" t="str">
-        <v>chuca</v>
+        <v>moucho</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>taburete</v>
+        <v>tachola</v>
       </c>
       <c r="B669" t="str">
-        <v>moucho</v>
+        <v>chatola</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>tachola</v>
+        <v>tachonar</v>
       </c>
       <c r="B670" t="str">
-        <v>chatola</v>
+        <v>chatolar</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>tachonar</v>
+        <v>tal vez</v>
       </c>
       <c r="B671" t="str">
-        <v>chatolar</v>
+        <v>talvez</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>tal vez</v>
+        <v>tambalear</v>
       </c>
       <c r="B672" t="str">
-        <v>talvez</v>
+        <v>cambalear</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>tambalear</v>
+        <v>tamiz</v>
       </c>
       <c r="B673" t="str">
-        <v>cambalear</v>
+        <v>baruto</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>tamiz</v>
+        <v>tanda</v>
       </c>
       <c r="B674" t="str">
-        <v>baruto</v>
+        <v>vez</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>tanda</v>
+        <v>tantear</v>
       </c>
       <c r="B675" t="str">
-        <v>vez</v>
+        <v>tentear</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>tantear</v>
+        <v>tarta</v>
       </c>
       <c r="B676" t="str">
-        <v>tentear</v>
+        <v>torta</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>tarta</v>
+        <v>tartrato</v>
       </c>
       <c r="B677" t="str">
-        <v>torta</v>
+        <v>tartarato</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>tartrato</v>
+        <v>tasa</v>
       </c>
       <c r="B678" t="str">
-        <v>tartarato</v>
+        <v>taxa</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>tasa</v>
+        <v>taza</v>
       </c>
       <c r="B679" t="str">
-        <v>taxa</v>
+        <v>cunca</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>taza</v>
+        <v>tenedor</v>
       </c>
       <c r="B680" t="str">
-        <v>cunca</v>
+        <v>garfo</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>tenedor</v>
+        <v>terciá</v>
       </c>
       <c r="B681" t="str">
-        <v>garfo</v>
+        <v>terzá</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>terciá</v>
+        <v>terciado</v>
       </c>
       <c r="B682" t="str">
-        <v>terzá</v>
+        <v>terzado</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>terciado</v>
+        <v>terciar</v>
       </c>
       <c r="B683" t="str">
-        <v>terzado</v>
+        <v>terzar</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>terciar</v>
+        <v>tercio</v>
       </c>
       <c r="B684" t="str">
-        <v>terzar</v>
+        <v>terzo</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>tercio</v>
+        <v>terno</v>
       </c>
       <c r="B685" t="str">
-        <v>terzo</v>
+        <v>tenro</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>terno</v>
+        <v>timar</v>
       </c>
       <c r="B686" t="str">
-        <v>tenro</v>
+        <v>estafar</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>timar</v>
+        <v>tina</v>
       </c>
       <c r="B687" t="str">
-        <v>estafar</v>
+        <v>talla</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>tina</v>
+        <v>tinte</v>
       </c>
       <c r="B688" t="str">
-        <v>talla</v>
+        <v>tinguidura</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>tinte</v>
+        <v>tiovivo</v>
       </c>
       <c r="B689" t="str">
-        <v>tinguidura</v>
+        <v>carrusel</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>tiovivo</v>
+        <v>tiza</v>
       </c>
       <c r="B690" t="str">
-        <v>carrusel</v>
+        <v>xiz</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>tiza</v>
+        <v>tizar</v>
       </c>
       <c r="B691" t="str">
-        <v>xiz</v>
+        <v>atizar</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>tizar</v>
+        <v>toca</v>
       </c>
       <c r="B692" t="str">
-        <v>atizar</v>
+        <v>touca</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>toca</v>
+        <v>tocado</v>
       </c>
       <c r="B693" t="str">
-        <v>touca</v>
+        <v>toucado</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>tocado</v>
+        <v>tocador</v>
       </c>
       <c r="B694" t="str">
-        <v>toucado</v>
+        <v>toucador</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>tocador</v>
+        <v>tornillo</v>
       </c>
       <c r="B695" t="str">
-        <v>toucador</v>
+        <v>parafuso</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>tornillo</v>
+        <v>tortícolis</v>
       </c>
       <c r="B696" t="str">
-        <v>parafuso</v>
+        <v>postura</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>tortícolis</v>
+        <v>tragaluz</v>
       </c>
       <c r="B697" t="str">
-        <v>postura</v>
+        <v>bufarda</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>tragaluz</v>
+        <v>traición</v>
       </c>
       <c r="B698" t="str">
-        <v>bufarda</v>
+        <v>traizón</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>traición</v>
+        <v>tramoia</v>
       </c>
       <c r="B699" t="str">
-        <v>traizón</v>
+        <v>tremoia</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>tramoia</v>
+        <v>trance</v>
       </c>
       <c r="B700" t="str">
-        <v>tremoia</v>
+        <v>transo</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>trance</v>
+        <v>transtornar</v>
       </c>
       <c r="B701" t="str">
-        <v>transo</v>
+        <v>trastornar</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>transtornar</v>
+        <v>trébol</v>
       </c>
       <c r="B702" t="str">
-        <v>trastornar</v>
+        <v>trevo</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>trébol</v>
+        <v>trending topic</v>
       </c>
       <c r="B703" t="str">
-        <v>trevo</v>
+        <v>tema do momento</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>trending topic</v>
+        <v>trineo</v>
       </c>
       <c r="B704" t="str">
-        <v>tema do momento</v>
+        <v>zorra</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>trineo</v>
+        <v>trino</v>
       </c>
       <c r="B705" t="str">
-        <v>zorra</v>
+        <v>trilo</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>trino</v>
+        <v>triple</v>
       </c>
       <c r="B706" t="str">
-        <v>trilo</v>
+        <v>triplo</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>triple</v>
+        <v>trisquel</v>
       </c>
       <c r="B707" t="str">
-        <v>triplo</v>
+        <v>tríscele</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>trisquel</v>
+        <v>trogallo</v>
       </c>
       <c r="B708" t="str">
-        <v>tríscele</v>
+        <v>torgallo</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>trogallo</v>
+        <v>troquel</v>
       </c>
       <c r="B709" t="str">
-        <v>torgallo</v>
+        <v>cuño</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>troquel</v>
+        <v>troquisto</v>
       </c>
       <c r="B710" t="str">
-        <v>cuño</v>
+        <v>trocisco</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>troquisto</v>
+        <v>troxo</v>
       </c>
       <c r="B711" t="str">
-        <v>trocisco</v>
+        <v>trocho</v>
       </c>
     </row>
     <row r="712">
@@ -14744,162 +14744,162 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>troxo</v>
+        <v>trozo</v>
       </c>
       <c r="B713" t="str">
-        <v>trocho</v>
+        <v>pedazo</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>trozo</v>
+        <v>tupé</v>
       </c>
       <c r="B714" t="str">
-        <v>pedazo</v>
+        <v>topete</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>tupé</v>
+        <v>turno</v>
       </c>
       <c r="B715" t="str">
-        <v>topete</v>
+        <v>quenda</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>turno</v>
+        <v>turón</v>
       </c>
       <c r="B716" t="str">
-        <v>quenda</v>
+        <v>tourón</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>turón</v>
+        <v>turreiro</v>
       </c>
       <c r="B717" t="str">
-        <v>tourón</v>
+        <v>terreiro</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>turreiro</v>
+        <v>ungüis</v>
       </c>
       <c r="B718" t="str">
-        <v>terreiro</v>
+        <v>ungüe</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>ungüis</v>
+        <v>uniformizar</v>
       </c>
       <c r="B719" t="str">
-        <v>ungüe</v>
+        <v>uniformar</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>uniformizar</v>
+        <v>urizo</v>
       </c>
       <c r="B720" t="str">
-        <v>uniformar</v>
+        <v>ourizo</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>urizo</v>
+        <v>vacío</v>
       </c>
       <c r="B721" t="str">
-        <v>ourizo</v>
+        <v>baleiro</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>vacío</v>
+        <v>vacuna</v>
       </c>
       <c r="B722" t="str">
-        <v>baleiro</v>
+        <v>vacina</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>vacuna</v>
+        <v>de vagar</v>
       </c>
       <c r="B723" t="str">
-        <v>vacina</v>
+        <v>devagar</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>de vagar</v>
+        <v>vela</v>
       </c>
       <c r="B724" t="str">
-        <v>devagar</v>
+        <v>candea</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>vela</v>
+        <v>veleta</v>
       </c>
       <c r="B725" t="str">
-        <v>candea</v>
+        <v>catavento</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>veleta</v>
+        <v>velro</v>
       </c>
       <c r="B726" t="str">
-        <v>catavento</v>
+        <v>vérrago</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>velro</v>
+        <v>vencello</v>
       </c>
       <c r="B727" t="str">
-        <v>vérrago</v>
+        <v>birrio</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>vencello</v>
+        <v>ventanilla</v>
       </c>
       <c r="B728" t="str">
-        <v>birrio</v>
+        <v>portelo</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>ventanilla</v>
+        <v>ventisca</v>
       </c>
       <c r="B729" t="str">
-        <v>portelo</v>
+        <v>xistra</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>ventisca</v>
+        <v>vereda</v>
       </c>
       <c r="B730" t="str">
-        <v>xistra</v>
+        <v>verea</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>vereda</v>
+        <v>veriño</v>
       </c>
       <c r="B731" t="str">
-        <v>verea</v>
+        <v>albeiro</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>veriño</v>
+        <v>verlo</v>
       </c>
       <c r="B732" t="str">
-        <v>albeiro</v>
+        <v>vérrago</v>
       </c>
     </row>
     <row r="733">
@@ -14907,268 +14907,260 @@
         <v>verlo</v>
       </c>
       <c r="B733" t="str">
-        <v>vérrago</v>
+        <v>vélaro</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>verlo</v>
+        <v>vertedeira</v>
       </c>
       <c r="B734" t="str">
-        <v>vélaro</v>
+        <v>veso</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>vertedeira</v>
+        <v>verxa</v>
       </c>
       <c r="B735" t="str">
-        <v>veso</v>
+        <v>enreixado</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>verxa</v>
+        <v>vestuario</v>
       </c>
       <c r="B736" t="str">
-        <v>enreixado</v>
+        <v>vestiario</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>vestuario</v>
+        <v>vicaría</v>
       </c>
       <c r="B737" t="str">
-        <v>vestiario</v>
+        <v>vigairía</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>vicaría</v>
+        <v>virrei</v>
       </c>
       <c r="B738" t="str">
-        <v>vigairía</v>
+        <v>vicerrei</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>virrei</v>
+        <v>viruta</v>
       </c>
       <c r="B739" t="str">
-        <v>vicerrei</v>
+        <v>labra</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>viruta</v>
+        <v>vitola</v>
       </c>
       <c r="B740" t="str">
-        <v>labra</v>
+        <v>bitola</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>vitola</v>
+        <v>vivaque</v>
       </c>
       <c r="B741" t="str">
-        <v>bitola</v>
+        <v>bivaque</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>vivaque</v>
+        <v>voladizo</v>
       </c>
       <c r="B742" t="str">
-        <v>bivaque</v>
+        <v>beiril</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>voladizo</v>
+        <v>xabalina</v>
       </c>
       <c r="B743" t="str">
-        <v>beiril</v>
+        <v>xavelina</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>xabalina</v>
+        <v>xábega</v>
       </c>
       <c r="B744" t="str">
-        <v>xavelina</v>
+        <v>xávega</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>xábega</v>
+        <v>xalea</v>
       </c>
       <c r="B745" t="str">
-        <v>xávega</v>
+        <v>xelea</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>xalea</v>
+        <v>xarrón</v>
       </c>
       <c r="B746" t="str">
-        <v>xelea</v>
+        <v>vaso</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>xarrón</v>
+        <v>xaula</v>
       </c>
       <c r="B747" t="str">
-        <v>vaso</v>
+        <v>gaiola</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>xaula</v>
+        <v>xenízaro</v>
       </c>
       <c r="B748" t="str">
-        <v>gaiola</v>
+        <v>xanízaro</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>xenízaro</v>
+        <v>xoroba</v>
       </c>
       <c r="B749" t="str">
-        <v>xanízaro</v>
+        <v>corcova</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>xoroba</v>
+        <v>xudía</v>
       </c>
       <c r="B750" t="str">
-        <v>corcova</v>
+        <v>feixón</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>xudía</v>
+        <v>xunca</v>
       </c>
       <c r="B751" t="str">
-        <v>feixón</v>
+        <v>engra</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>xunca</v>
+        <v>zampar</v>
       </c>
       <c r="B752" t="str">
-        <v>engra</v>
+        <v>papar</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>zampar</v>
+        <v>zángano</v>
       </c>
       <c r="B753" t="str">
-        <v>papar</v>
+        <v>abázcaro</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>zángano</v>
+        <v>zanxa</v>
       </c>
       <c r="B754" t="str">
-        <v>abázcaro</v>
+        <v>gabia</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>zanxa</v>
+        <v>zar</v>
       </c>
       <c r="B755" t="str">
-        <v>gabia</v>
+        <v>tsar</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>zar</v>
+        <v>zarrapo</v>
       </c>
       <c r="B756" t="str">
-        <v>tsar</v>
+        <v>farrapo</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>zarrapo</v>
+        <v>zendo</v>
       </c>
       <c r="B757" t="str">
-        <v>farrapo</v>
+        <v>cendo</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>zendo</v>
+        <v>zeolita</v>
       </c>
       <c r="B758" t="str">
-        <v>cendo</v>
+        <v>ceolita</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>zeolita</v>
+        <v>zepelín</v>
       </c>
       <c r="B759" t="str">
-        <v>ceolita</v>
+        <v>cepelín</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>zepelín</v>
+        <v>zeugma</v>
       </c>
       <c r="B760" t="str">
-        <v>cepelín</v>
+        <v>ceugma</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>zeugma</v>
+        <v>zigurat</v>
       </c>
       <c r="B761" t="str">
-        <v>ceugma</v>
+        <v>cigurat</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>zigurat</v>
+        <v>zinxiberáceas</v>
       </c>
       <c r="B762" t="str">
-        <v>cigurat</v>
+        <v>cinxiberáceas</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>zinxiberáceas</v>
+        <v>zócalo</v>
       </c>
       <c r="B763" t="str">
-        <v>cinxiberáceas</v>
+        <v>zócolo</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>zócalo</v>
+        <v>zuleiro</v>
       </c>
       <c r="B764" t="str">
-        <v>zócolo</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="str">
-        <v>zuleiro</v>
-      </c>
-      <c r="B765" t="str">
         <v>celeiro</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B765"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B764"/>
   </ignoredErrors>
 </worksheet>
 </file>
